--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3016" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3030" uniqueCount="340">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -454,6 +454,9 @@
 </t>
   </si>
   <si>
+    <t>Can serve as a target of a linkHtml reference</t>
+  </si>
+  <si>
     <t>Section.classCode</t>
   </si>
   <si>
@@ -643,6 +646,9 @@
     <t>Titre de la section</t>
   </si>
   <si>
+    <t>If valued, it is to be rendered as part of the narrative content of the clinical document body.</t>
+  </si>
+  <si>
     <t>Section.text</t>
   </si>
   <si>
@@ -653,10 +659,25 @@
     <t>Bloc narratif de la section</t>
   </si>
   <si>
+    <t>Also referred to as the CDA Narrative Block</t>
+  </si>
+  <si>
     <t>Section.confidentialityCode</t>
   </si>
   <si>
+    <t>Controls the disclosure of information in this section</t>
+  </si>
+  <si>
+    <t>A value for Section.confidentialityCode overrides the value propagated from StructuredBody.</t>
+  </si>
+  <si>
     <t>Section.languageCode</t>
+  </si>
+  <si>
+    <t>Human language of character data</t>
+  </si>
+  <si>
+    <t>A value for Section.languageCode overrides the value propagated from StructuredBody.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/all-languages</t>
@@ -669,6 +690,15 @@
 </t>
   </si>
   <si>
+    <t>Primary target of the entries recorded in a section</t>
+  </si>
+  <si>
+    <t>Most of the time the subject is the same as the recordTarget, but need not be, for instance when the subject is a fetus observed in an obstetrical ultrasound.</t>
+  </si>
+  <si>
+    <t>The subject participant can be ascribed to a CDA section or a CDA entry. It propagates to nested components, unless overridden. The subject of a document is presumed to be the patient.</t>
+  </si>
+  <si>
     <t>Section.author</t>
   </si>
   <si>
@@ -676,6 +706,9 @@
 </t>
   </si>
   <si>
+    <t>The author participant can be ascribed to a CDA section, where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.informant</t>
   </si>
   <si>
@@ -683,6 +716,9 @@
 </t>
   </si>
   <si>
+    <t>The informant participant can be ascribed to a CDA section where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.entry</t>
   </si>
   <si>
@@ -986,6 +1022,12 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
 </t>
+  </si>
+  <si>
+    <t>Used to nest a Section within a Section</t>
+  </si>
+  <si>
+    <t>Context propagates to nested sections</t>
   </si>
   <si>
     <t>Section.component.nullFlavor</t>
@@ -1362,7 +1404,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="148.87109375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -3165,7 +3207,9 @@
       <c r="K18" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="L18" s="2"/>
+      <c r="L18" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3236,10 +3280,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3273,7 +3317,7 @@
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>74</v>
@@ -3295,7 +3339,7 @@
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>74</v>
@@ -3313,7 +3357,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3333,10 +3377,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3370,7 +3414,7 @@
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>74</v>
@@ -3392,7 +3436,7 @@
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>74</v>
@@ -3410,7 +3454,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3430,10 +3474,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3447,7 +3491,7 @@
         <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>74</v>
@@ -3459,10 +3503,10 @@
         <v>95</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3513,7 +3557,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3533,10 +3577,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3550,7 +3594,7 @@
         <v>75</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>74</v>
@@ -3559,13 +3603,13 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3616,7 +3660,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3636,10 +3680,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3737,10 +3781,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3769,7 +3813,7 @@
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3781,7 +3825,7 @@
         <v>74</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>74</v>
@@ -3820,7 +3864,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3840,17 +3884,17 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>75</v>
@@ -3872,7 +3916,7 @@
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3884,7 +3928,7 @@
         <v>74</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>74</v>
@@ -3923,7 +3967,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3943,17 +3987,17 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>80</v>
@@ -3975,7 +4019,7 @@
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3987,7 +4031,7 @@
         <v>74</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>74</v>
@@ -4026,7 +4070,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4046,17 +4090,17 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>80</v>
@@ -4078,7 +4122,7 @@
       </c>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4129,7 +4173,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4149,17 +4193,17 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>75</v>
@@ -4181,7 +4225,7 @@
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4193,7 +4237,7 @@
         <v>74</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>74</v>
@@ -4232,7 +4276,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4252,10 +4296,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4278,11 +4322,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4333,7 +4377,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4353,10 +4397,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4383,7 +4427,7 @@
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4434,7 +4478,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4454,17 +4498,17 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>80</v>
@@ -4482,11 +4526,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4537,7 +4581,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4557,17 +4601,17 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4585,11 +4629,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4640,7 +4684,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4660,17 +4704,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -4688,11 +4732,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4743,7 +4787,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4763,10 +4807,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4780,7 +4824,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4789,16 +4833,18 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+      <c r="O34" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>74</v>
       </c>
@@ -4846,7 +4892,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4866,10 +4912,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4883,7 +4929,7 @@
         <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>74</v>
@@ -4892,15 +4938,17 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>74</v>
@@ -4949,7 +4997,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4969,10 +5017,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4995,12 +5043,16 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="L36" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>74</v>
       </c>
@@ -5048,7 +5100,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5068,10 +5120,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5096,10 +5148,14 @@
       <c r="K37" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L37" s="2"/>
+      <c r="L37" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>74</v>
       </c>
@@ -5127,7 +5183,7 @@
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>74</v>
@@ -5145,7 +5201,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5165,10 +5221,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5191,12 +5247,18 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="L38" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+      <c r="N38" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>74</v>
       </c>
@@ -5244,7 +5306,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5264,10 +5326,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5290,12 +5352,14 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>74</v>
       </c>
@@ -5343,7 +5407,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5363,10 +5427,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5389,12 +5453,14 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>74</v>
       </c>
@@ -5442,7 +5508,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5462,10 +5528,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5479,7 +5545,7 @@
         <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -5488,7 +5554,7 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -5529,7 +5595,7 @@
         <v>74</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
@@ -5539,7 +5605,7 @@
         <v>123</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5559,13 +5625,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>74</v>
@@ -5587,7 +5653,7 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
@@ -5640,7 +5706,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5660,10 +5726,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5761,10 +5827,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5862,10 +5928,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5963,10 +6029,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6064,10 +6130,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6167,10 +6233,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6270,10 +6336,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6373,10 +6439,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6476,10 +6542,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6577,10 +6643,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6610,7 +6676,7 @@
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
@@ -6636,7 +6702,7 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>74</v>
@@ -6654,7 +6720,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6674,10 +6740,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6711,7 +6777,7 @@
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="S53" t="s" s="2">
         <v>74</v>
@@ -6753,7 +6819,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6773,10 +6839,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6799,7 +6865,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6852,7 +6918,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6872,10 +6938,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6898,7 +6964,7 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -6951,7 +7017,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -6971,10 +7037,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6997,13 +7063,13 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7054,7 +7120,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7074,10 +7140,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7100,7 +7166,7 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -7153,7 +7219,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7173,10 +7239,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7199,7 +7265,7 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -7252,7 +7318,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7272,10 +7338,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7298,7 +7364,7 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -7351,7 +7417,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7371,10 +7437,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7397,7 +7463,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7450,7 +7516,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7470,10 +7536,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7496,7 +7562,7 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -7549,7 +7615,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7569,10 +7635,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7595,7 +7661,7 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -7648,7 +7714,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7668,13 +7734,13 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>74</v>
@@ -7696,7 +7762,7 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -7749,7 +7815,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7769,10 +7835,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7870,10 +7936,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7971,10 +8037,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8072,10 +8138,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8173,10 +8239,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8276,10 +8342,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8379,10 +8445,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8482,10 +8548,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8585,10 +8651,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8686,10 +8752,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8719,7 +8785,7 @@
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
@@ -8745,7 +8811,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>74</v>
@@ -8763,7 +8829,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8783,10 +8849,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8820,7 +8886,7 @@
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>74</v>
@@ -8862,7 +8928,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8882,10 +8948,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8908,7 +8974,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -8961,7 +9027,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -8981,10 +9047,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9007,7 +9073,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9060,7 +9126,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9080,10 +9146,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9106,7 +9172,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9159,7 +9225,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9179,10 +9245,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9205,7 +9271,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9258,7 +9324,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9278,10 +9344,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9304,10 +9370,10 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
@@ -9359,7 +9425,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9379,10 +9445,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9405,7 +9471,7 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9458,7 +9524,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9478,10 +9544,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9504,7 +9570,7 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -9557,7 +9623,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9577,10 +9643,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9603,7 +9669,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -9656,7 +9722,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9676,10 +9742,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9702,7 +9768,7 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -9755,7 +9821,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -9775,10 +9841,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9801,12 +9867,16 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="L84" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+      <c r="O84" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>74</v>
       </c>
@@ -9854,7 +9924,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -9874,10 +9944,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9975,10 +10045,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10076,10 +10146,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10177,10 +10247,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10278,10 +10348,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10381,10 +10451,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10484,10 +10554,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10587,10 +10657,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10690,10 +10760,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10791,10 +10861,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10821,7 +10891,7 @@
       </c>
       <c r="L94" s="2"/>
       <c r="M94" t="s" s="2">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -10830,7 +10900,7 @@
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="S94" t="s" s="2">
         <v>74</v>
@@ -10872,7 +10942,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -10892,10 +10962,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -10929,7 +10999,7 @@
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="S95" t="s" s="2">
         <v>74</v>
@@ -10971,7 +11041,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -10991,10 +11061,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11017,7 +11087,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11070,7 +11140,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>75</v>

--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
